--- a/templates/휴무일정표.xlsx
+++ b/templates/휴무일정표.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/190e29534d76321d/Desktop/project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/190e29534d76321d/Desktop/project/jsec/jsec-fe/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{54AACDBA-D3EB-4ED6-B587-1A7297ADEA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50E8A74A-6D07-4C5F-A8AD-EF6DC5EEB001}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{54AACDBA-D3EB-4ED6-B587-1A7297ADEA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E31B6C37-3829-4697-AB47-84BFFE454D3D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{27C69C99-ABE1-4C31-976A-AC2C61E38B6B}"/>
   </bookViews>
@@ -1648,7 +1648,7 @@
       <c r="AF6" s="8"/>
       <c r="AG6" s="8"/>
       <c r="AH6" s="7" cm="1">
-        <f t="array" ref="AH6">SUMPRODUCT((C6:AG6="휴") + (C6:AG6="연") + (C6:AG6="공")) + SUM(C6:AG6)</f>
+        <f t="array" ref="AH6">SUMPRODUCT((C6:AG6="휴") + (C6:AG6="연") + (C6:AG6="공"))</f>
         <v>0</v>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       <c r="AF7" s="8"/>
       <c r="AG7" s="8"/>
       <c r="AH7" s="7" cm="1">
-        <f t="array" ref="AH7">SUMPRODUCT((C7:AG7="휴") + (C7:AG7="연") + (C7:AG7="공")) + SUM(C7:AG7)</f>
+        <f t="array" ref="AH7">SUMPRODUCT((C7:AG7="휴") + (C7:AG7="연") + (C7:AG7="공"))</f>
         <v>0</v>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AF9" s="8"/>
       <c r="AG9" s="8"/>
       <c r="AH9" s="7" cm="1">
-        <f t="array" ref="AH9">SUMPRODUCT((C9:AG9="휴") + (C9:AG9="연") + (C9:AG9="공")) + SUM(C9:AG9)</f>
+        <f t="array" ref="AH9">SUMPRODUCT((C9:AG9="휴") + (C9:AG9="연") + (C9:AG9="공"))</f>
         <v>0</v>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       <c r="AF10" s="8"/>
       <c r="AG10" s="8"/>
       <c r="AH10" s="7" cm="1">
-        <f t="array" ref="AH10">SUMPRODUCT((C10:AG10="휴") + (C10:AG10="연") + (C10:AG10="공")) + SUM(C10:AG10)</f>
+        <f t="array" ref="AH10">SUMPRODUCT((C10:AG10="휴") + (C10:AG10="연") + (C10:AG10="공"))</f>
         <v>0</v>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       <c r="AF11" s="8"/>
       <c r="AG11" s="8"/>
       <c r="AH11" s="7" cm="1">
-        <f t="array" ref="AH11">SUMPRODUCT((C11:AG11="휴") + (C11:AG11="연") + (C11:AG11="공")) + SUM(C11:AG11)</f>
+        <f t="array" ref="AH11">SUMPRODUCT((C11:AG11="휴") + (C11:AG11="연") + (C11:AG11="공"))</f>
         <v>0</v>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       <c r="AF13" s="8"/>
       <c r="AG13" s="8"/>
       <c r="AH13" s="7" cm="1">
-        <f t="array" ref="AH13">SUMPRODUCT((C13:AG13="휴") + (C13:AG13="연") + (C13:AG13="공")) + SUM(C13:AG13)</f>
+        <f t="array" ref="AH13">SUMPRODUCT((C13:AG13="휴") + (C13:AG13="연") + (C13:AG13="공"))</f>
         <v>0</v>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       <c r="AF15" s="8"/>
       <c r="AG15" s="8"/>
       <c r="AH15" s="7" cm="1">
-        <f t="array" ref="AH15">SUMPRODUCT((C15:AG15="휴") + (C15:AG15="연") + (C15:AG15="공")) + SUM(C15:AG15)</f>
+        <f t="array" ref="AH15">SUMPRODUCT((C15:AG15="휴") + (C15:AG15="연") + (C15:AG15="공"))</f>
         <v>0</v>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
       <c r="AF16" s="8"/>
       <c r="AG16" s="8"/>
       <c r="AH16" s="7" cm="1">
-        <f t="array" ref="AH16">SUMPRODUCT((C16:AG16="휴") + (C16:AG16="연") + (C16:AG16="공")) + SUM(C16:AG16)</f>
+        <f t="array" ref="AH16">SUMPRODUCT((C16:AG16="휴") + (C16:AG16="연") + (C16:AG16="공"))</f>
         <v>0</v>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       <c r="AF18" s="8"/>
       <c r="AG18" s="8"/>
       <c r="AH18" s="7" cm="1">
-        <f t="array" ref="AH18">SUMPRODUCT((C18:AG18="휴") + (C18:AG18="연") + (C18:AG18="공")) + SUM(C18:AG18)</f>
+        <f t="array" ref="AH18">SUMPRODUCT((C18:AG18="휴") + (C18:AG18="연") + (C18:AG18="공"))</f>
         <v>0</v>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       <c r="AF19" s="8"/>
       <c r="AG19" s="8"/>
       <c r="AH19" s="7" cm="1">
-        <f t="array" ref="AH19">SUMPRODUCT((C19:AG19="휴") + (C19:AG19="연") + (C19:AG19="공")) + SUM(C19:AG19)</f>
+        <f t="array" ref="AH19">SUMPRODUCT((C19:AG19="휴") + (C19:AG19="연") + (C19:AG19="공"))</f>
         <v>0</v>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       <c r="AF20" s="8"/>
       <c r="AG20" s="8"/>
       <c r="AH20" s="7" cm="1">
-        <f t="array" ref="AH20">SUMPRODUCT((C20:AG20="휴") + (C20:AG20="연") + (C20:AG20="공")) + SUM(C20:AG20)</f>
+        <f t="array" ref="AH20">SUMPRODUCT((C20:AG20="휴") + (C20:AG20="연") + (C20:AG20="공"))</f>
         <v>0</v>
       </c>
     </row>

--- a/templates/휴무일정표.xlsx
+++ b/templates/휴무일정표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/190e29534d76321d/Desktop/project/jsec/jsec-fe/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{54AACDBA-D3EB-4ED6-B587-1A7297ADEA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E31B6C37-3829-4697-AB47-84BFFE454D3D}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{54AACDBA-D3EB-4ED6-B587-1A7297ADEA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0017DDC-D730-457C-8EA4-D808BE65C68B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{27C69C99-ABE1-4C31-976A-AC2C61E38B6B}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{27C69C99-ABE1-4C31-976A-AC2C61E38B6B}"/>
   </bookViews>
   <sheets>
     <sheet name="직원근무표" sheetId="2" r:id="rId1"/>
@@ -933,6 +933,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
